--- a/checklist_forms/042_stormwater_inspection_form--checklist_forms.xlsx
+++ b/checklist_forms/042_stormwater_inspection_form--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>stormwater_system</t>
+          <t>Stormwater System</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>system_functioning</t>
+          <t>System Functioning</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,137 +589,118 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>system_functioning</t>
+          <t>stormwater_system_components</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>system_functioning</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Stormwater System Components</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please list all system components</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>inspection_results</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Inspection Results</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>recent_damage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Recent Damage</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>system_functioning</t>
+          <t>maintenance_planned</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>System Functioning</t>
+          <t>Maintenance Planned</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>system_functioning</t>
+          <t>regulatory_compliance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>System Functioning</t>
+          <t>Regulatory Compliance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>inspection_results</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Inspection Results</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A brief description of the inspection results</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -734,12 +715,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -784,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -801,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>system_is_functioning_as_expected</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>System is functioning as expected</t>
         </is>
       </c>
     </row>
@@ -818,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>system_is_malfunctioning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>System is malfunctioning</t>
         </is>
       </c>
     </row>
@@ -835,165 +816,199 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no_issues_reported</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No issues reported</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>system_functioning_choices</t>
+          <t>stormwater_system_components_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pipes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pipes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>stormwater_system_components_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pumps</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pumps</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>stormwater_system_components_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>valves</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Valves</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>stormwater_system_components_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>motors</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Motors</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>recent_damage_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>system_functioning_choices</t>
+          <t>recent_damage_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>system_functioning_choices</t>
+          <t>maintenance_planned_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>system_functioning_choices</t>
+          <t>maintenance_planned_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>system_functioning_choices</t>
+          <t>regulatory_compliance_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>regulatory_compliance_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>regulatory_compliance_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>partially_compliant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Partially compliant</t>
         </is>
       </c>
     </row>
